--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_826_United_Kingdom_UK.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_826_United_Kingdom_UK.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rc79c1fcca5924082"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R02f3c7fb1eb24eee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rde2ef5f2865b4976"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R1c43ccb78fc14805"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R29b2eb05630d414c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R2b2d6f7336d44b36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R9cdf8e157db247f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rcb940b6270724304"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R23bf84036e854bab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R2dd1d59d41b74903"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R12dbdf5077a14539"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Ra4d2a5867f354eb5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ826CommercialTable" displayName="EEZ826CommercialTable" ref="A1:O13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O13"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ826CommercialTable" displayName="EEZ826CommercialTable" ref="A1:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E13"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ826FunctionalTable" displayName="EEZ826FunctionalTable" ref="A1:O27" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O27"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ826FunctionalTable" displayName="EEZ826FunctionalTable" ref="A1:E27" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E27"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ826ValidationTable" displayName="EEZ826ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ826ValidationTable" displayName="EEZ826ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -23876,7 +23830,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96289cf1f16c4d75"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae4f077ec9ac4400"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23886,20 +23840,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -23907,714 +23851,250 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>916.7675650399</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>916.7675650399</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$347,A2,'Species'!$U$2:$U$347))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>118102.54046694569</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>118102.54046694569</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>376961.5970546267</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.101860199952847</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1264.3292924573348</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>376961.5970546267</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1450.558805478172</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$347,A3,'Species'!$U$2:$U$347))</x:f>
-        <x:v>546804963.9347032</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.101860199952847</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1264.3292924573348</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>476603589.28766304</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>70201374.64704019</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.1472951027329943</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.14729510273299437</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>98966.5879995493</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.041927858516348</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>110.13563459450836</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>98966.5879995493</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>124.67012672763023</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$347,A4,'Species'!$U$2:$U$347))</x:f>
-        <x:v>12338177.067704981</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.041927858516348</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>110.13563459450836</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>10899747.972983617</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>1438429.0947213639</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.1319690233468416</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.13196902334684155</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>95341.55794298879</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.3607123310181057</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>229.46282234748207</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>95341.55794298879</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>337.2682109734274</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$347,A5,'Species'!$U$2:$U$347))</x:f>
-        <x:v>32155676.6788512</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.3607123310181057</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>229.46282234748207</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>21877342.972604204</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>10278333.706246994</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.469816362943068</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.469816362943068</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>321053.3533330292</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.2772625625795544</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>189.34880238043124</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>321053.3533330292</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>201.46253771019582</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$347,A6,'Species'!$U$2:$U$347))</x:f>
-        <x:v>64680223.30284022</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.2772625625795544</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>189.34880238043124</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>60791067.95383051</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>3889155.3490097076</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0639757694660577</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.06397576946605768</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>104444.99463952529</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.4593537427281715</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>28.797430759156274</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>104444.99463952529</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>154.00076318241494</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$347,A7,'Species'!$U$2:$U$347))</x:f>
-        <x:v>16084608.885070132</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.4593537427281715</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>28.797430759156274</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>3007747.501272178</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>13076861.383797955</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>5.347725790900624</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>4.347725790900624</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>332730.3585981146</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.4023432616589977</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>252.54760928124932</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>332730.3585981146</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>441.14123988136504</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$347,A8,'Species'!$U$2:$U$347))</x:f>
-        <x:v>146781082.93814346</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.4023432616589977</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>252.54760928124932</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>84030256.59924662</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>62750826.33889684</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.746764664044349</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.7467646640443489</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>346155.27542369766</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.6375612625573135</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>434.07149042788234</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>346155.27542369766</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>445.8183320116454</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$347,A9,'Species'!$U$2:$U$347))</x:f>
-        <x:v>154322367.5064246</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.6375612625573135</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>434.07149042788234</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>150256136.32263854</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>4066231.1837860644</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0270619974884407</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.027061997488440813</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>10670.2681171143</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.363704982182091</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>231.04947295058935</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>10670.2681171143</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>236.6176151444807</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$347,A10,'Species'!$U$2:$U$347))</x:f>
-        <x:v>2524773.394823774</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.363704982182091</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>231.04947295058935</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>2465359.8247007364</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>59413.57012303779</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0240993503373286</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.024099350337328487</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>9284.417181474802</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.8455491026882553</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>700.7274048120449</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>9284.417181474802</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>718.2400798860001</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$347,A11,'Species'!$U$2:$U$347))</x:f>
-        <x:v>6668440.538117414</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.8455491026882553</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>700.7274048120449</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>6505845.556767199</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>162594.98135021515</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0249921366763908</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.024992136676390723</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>17137.2702349019</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.923540976404151</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>838.5731956601669</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>17137.2702349019</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>921.6655150754797</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$347,A12,'Species'!$U$2:$U$347))</x:f>
-        <x:v>15794830.998038545</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.923540976404151</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>838.5731956601669</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>14370855.465773543</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>1423975.532265002</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0990877359845712</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.09908773598457127</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>602.3012277857</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.445810370118448</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>2791.324774024404</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>602.3012277857</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2890.845789334684</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$H$2:$H$347,A13,'Species'!$U$2:$U$347))</x:f>
-        <x:v>1741159.9682554014</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.445810370118448</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>2791.324774024404</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>1681218.3385435403</x:v>
       </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>59941.629711861024</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0356536853885314</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.035653685388531496</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G13">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O13">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4b70451144343ea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61252e038bf641b8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24624,20 +24104,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -24645,1470 +24115,516 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>14318.099974202702</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.89089167422049</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>777.8425101087406</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>14318.099974202702</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>924.4051118456066</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$347,A2,'Species'!$U$2:$U$347))</x:f>
-        <x:v>13235724.808069425</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.89089167422049</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>777.8425101087406</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>11137226.823921723</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>2098497.9841477014</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.1884219489577355</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.18842194895773548</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>3465.6304135993996</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.423892985568667</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2653.951521643116</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>3465.6304135993996</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2678.510200597228</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$347,A3,'Species'!$U$2:$U$347))</x:f>
-        <x:v>9282726.414325982</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.423892985568667</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2653.951521643116</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>9197615.109624788</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>85111.30470119417</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.009253627563968</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.009253627563968182</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>188.50520784309998</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.5412028630384302</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>347.6985367744788</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>188.50520784309998</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>348.2800155839514</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$347,A4,'Species'!$U$2:$U$347))</x:f>
-        <x:v>65652.59672525086</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.5412028630384302</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>347.6985367744788</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>65542.98494141486</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>109.61178383599326</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0016723648447499</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0016723648447498842</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>39943.126257230004</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.113090405930141</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1297.4493294591614</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>39943.126257230004</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1330.0451495719005</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$347,A5,'Species'!$U$2:$U$347))</x:f>
-        <x:v>53126161.337166786</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.113090405930141</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1297.4493294591614</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>51824182.37894569</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>1301978.9582210928</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0251230004691794</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.025123000469179427</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>62526.386074865295</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.3361807372400625</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2168.6064105315386</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>62526.386074865295</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2250.7615678356497</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$347,A6,'Species'!$U$2:$U$347))</x:f>
-        <x:v>140731986.75296095</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.3361807372400625</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2168.6064105315386</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>135595121.66932282</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>5136865.083638132</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0378838487727122</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.03788384877271216</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>49477.8065186399</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.3122254691398267</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>205.22273405108623</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>49477.8065186399</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>278.05829426701735</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$347,A7,'Species'!$U$2:$U$347))</x:f>
-        <x:v>13757714.484646523</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.3122254691398267</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>205.22273405108623</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>10153970.728605937</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>3603743.756040586</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.3549098035006206</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.35490980350062057</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>31.6828635908</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.319032537900649</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>2084.6470616832826</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>31.6828635908</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>2394.115267800872</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$347,A8,'Species'!$U$2:$U$347))</x:f>
-        <x:v>75852.42745038665</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.319032537900649</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>2084.6470616832826</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>66047.58849027347</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>9804.838960113178</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.1484511271983395</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.1484511271983396</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>4483.4163492866</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.8335254023564427</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>681.5934407022149</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>4483.4163492866</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>706.8427285433057</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$347,A9,'Species'!$U$2:$U$347))</x:f>
-        <x:v>3169070.245525407</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.8335254023564427</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>681.5934407022149</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>3055867.175610817</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>113203.0699145901</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0370444994527495</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.03704449945274951</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>487.21637249070005</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.372034756355867</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>235.5237764776649</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>487.21637249070005</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>271.8689405631871</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$347,A10,'Species'!$U$2:$U$347))</x:f>
-        <x:v>132458.99901408577</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.372034756355867</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>235.5237764776649</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>114751.04001075837</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>17707.9590033274</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.1543163269079497</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.15431632690794966</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>6070.1541293468</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.025090042906532</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1059.4733645609037</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>6070.1541293468</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1169.0001480912917</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$347,A11,'Species'!$U$2:$U$347))</x:f>
-        <x:v>7096011.076143375</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.025090042906532</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1059.4733645609037</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>6431166.618822318</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>664844.4573210571</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.1033785153964497</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.10337851539644982</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>75994.71924031261</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.0049556248499676</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>101.14760988209572</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>75994.71924031261</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>117.23789857855743</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$347,A12,'Species'!$U$2:$U$347))</x:f>
-        <x:v>8909461.186801717</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.0049556248499676</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>101.14760988209572</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>7686684.2148185335</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>1222776.9719831832</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.1590773001479482</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.15907730014794816</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>32130.894872365403</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.121092860524776</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>1321.5781828475156</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>32130.894872365403</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>2078.777002829363</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$347,A13,'Species'!$U$2:$U$347))</x:f>
-        <x:v>66792965.3410011</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.121092860524776</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>1321.5781828475156</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>42463489.65868522</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>24329475.68231588</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.572950454092971</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.5729504540929711</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>87.7741549414</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.9523727401778017</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>896.1335565312186</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>87.7741549414</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>954.796904722396</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$347,A14,'Species'!$U$2:$U$347))</x:f>
-        <x:v>83806.49145267272</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.9523727401778017</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>896.1335565312186</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>78657.36563915902</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>5149.125813513703</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0654627290358964</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.0654627290358965</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>246626.03514493065</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>4.048637294477852</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>1118.5033636479802</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>246626.03514493065</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>1323.5257744100734</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$347,A15,'Species'!$U$2:$U$347))</x:f>
-        <x:v>326415914.1548803</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>4.048637294477852</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>1118.5033636479802</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>275852049.8727699</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>50563864.28211039</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.18330066535823</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.18330066535823009</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>335866.61490539095</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.371675555626753</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>235.32905759599504</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>335866.61490539095</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>293.331105516559</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$347,A16,'Species'!$U$2:$U$347))</x:f>
-        <x:v>98520125.45630272</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.371675555626753</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>235.32905759599504</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>79039173.96364263</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>19480951.49266009</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.2464721038408266</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.24647210384082668</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>568724.2782547415</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.5350615399438663</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>342.81636051136707</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>568724.2782547415</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>361.0036593206311</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$347,A17,'Species'!$U$2:$U$347))</x:f>
-        <x:v>205311545.59444648</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.5350615399438663</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>342.81636051136707</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>194967987.20574448</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>10343558.388702005</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0530525987211774</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.05305259872117737</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>388.5817676145</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.1561730798345096</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>143.27587843664728</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>388.5817676145</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>181.2806397818224</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$347,A18,'Species'!$U$2:$U$347))</x:f>
-        <x:v>70442.351440708</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.1561730798345096</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>143.27587843664728</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>55674.394099432626</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>14767.957341275367</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.2652558250548769</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.2652558250548768</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>105403.3849815726</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>2.4632665720290063</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>29.0580570461794</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>105403.3849815726</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>153.38127573667052</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$347,A19,'Species'!$U$2:$U$347))</x:f>
-        <x:v>16166905.655437022</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>2.4632665720290063</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>29.0580570461794</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>3062817.5736549455</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>13104088.081782077</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>5.278442240405655</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>4.278442240405655</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>22971.8687592367</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.1642380870228526</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>145.96142243099544</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>22971.8687592367</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>149.25715956498414</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$347,A20,'Species'!$U$2:$U$347))</x:f>
-        <x:v>3428715.880903266</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.1642380870228526</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>145.96142243099544</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>3353006.639996335</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>75709.240906931</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.022579508195371</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.02257950819537111</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small bathydemersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>16.256817468999998</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.54</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>346.73685045253166</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>16.256817468999998</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>346.73685045253166</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$347,A21,'Species'!$U$2:$U$347))</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>5636.837687582756</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.54</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>346.73685045253166</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
-        <x:v>5636.837687582756</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>660.6786744673</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.140214533637862</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>138.10663179697764</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>660.6786744673</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>138.19906057130083</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$347,A22,'Species'!$U$2:$U$347))</x:f>
-        <x:v>91305.17215087313</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.140214533637862</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>138.10663179697764</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>91244.10643077065</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>61.06572010247328</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.000669256596302</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.0006692565963019811</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>91899.14307469298</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.0182660265239387</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>104.29560951753626</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>91899.14307469298</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>104.45843894827357</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$347,A23,'Species'!$U$2:$U$347))</x:f>
-        <x:v>9599641.026266474</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.0182660265239387</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>104.29560951753626</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>9584677.141114376</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>14963.885152097791</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.0015612299644303</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.001561229964430288</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>55.0433283998</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.454405603217681</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>284.7118892764299</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>55.0433283998</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>306.5147504136475</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$347,A24,'Species'!$U$2:$U$347))</x:f>
-        <x:v>16871.592066401132</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.454405603217681</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>284.7118892764299</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>15671.490020770025</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>1200.102045631107</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1.0765786816722958</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0.07657868167229574</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>45863.75142434889</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.413019948607274</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>258.83318032139664</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>45863.75142434889</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>401.1438581196668</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$347,A25,'Species'!$U$2:$U$347))</x:f>
-        <x:v>18397962.194204677</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.413019948607274</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>258.83318032139664</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>11871060.64263421</x:v>
-      </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>6526901.551570468</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.5498162083453173</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>0.5498162083453174</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="18" customHeight="1">
       <x:c r="A26" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B26" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D26" s="31" t="n">
+      <x:c r="B26" s="31" t="n">
         <x:v>2754.9971113934</x:v>
       </x:c>
+      <x:c r="C26" s="32" t="n">
+        <x:v>3.9862106572298988</x:v>
+      </x:c>
+      <x:c r="D26" s="32" t="n">
+        <x:f>IF(C26="","",(1/'Metadata'!$B$5)^(C26-1))</x:f>
+        <x:v>968.7476393625249</x:v>
+      </x:c>
       <x:c r="E26" s="31" t="n">
-        <x:v>2754.9971113934</x:v>
-      </x:c>
-      <x:c r="F26" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H26" s="32" t="n">
-        <x:f>IF(E26=0,"",I26/E26)</x:f>
-        <x:v>1082.0652947970482</x:v>
-      </x:c>
-      <x:c r="I26" s="31" t="n">
-        <x:f>IF(C26=0,"",SUMIF('Species'!$G$2:$G$347,A26,'Species'!$U$2:$U$347))</x:f>
-        <x:v>2981086.7615049155</x:v>
-      </x:c>
-      <x:c r="J26" s="32" t="n">
-        <x:v>3.9862106572298988</x:v>
-      </x:c>
-      <x:c r="K26" s="32" t="n">
-        <x:f>IF(J26="","",(1/'Metadata'!$B$5)^(J26-1))</x:f>
-        <x:v>968.7476393625249</x:v>
-      </x:c>
-      <x:c r="L26" s="31" t="n">
-        <x:f>IF(E26=0,"",E26*K26)</x:f>
+        <x:f>IF(B26=0,"",B26*D26)</x:f>
         <x:v>2668896.948112931</x:v>
-      </x:c>
-      <x:c r="M26" s="31" t="n">
-        <x:f>IF(E26=0,"",I26-L26)</x:f>
-        <x:v>312189.81339198444</x:v>
-      </x:c>
-      <x:c r="N26" s="32" t="n">
-        <x:f>IF(L26=0,"",I26/L26)</x:f>
-        <x:v>1.1169733487134905</x:v>
-      </x:c>
-      <x:c r="O26" s="34" t="n">
-        <x:f>IF(L26=0,"",M26/L26)</x:f>
-        <x:v>0.1169733487134905</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="18" customHeight="1">
       <x:c r="A27" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B27" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C27" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D27" s="31" t="n">
+      <x:c r="B27" s="31" t="n">
         <x:v>3828.7026448751003</x:v>
       </x:c>
+      <x:c r="C27" s="32" t="n">
+        <x:v>3.8228551790498573</x:v>
+      </x:c>
+      <x:c r="D27" s="32" t="n">
+        <x:f>IF(C27="","",(1/'Metadata'!$B$5)^(C27-1))</x:f>
+        <x:v>665.0513494955133</x:v>
+      </x:c>
       <x:c r="E27" s="31" t="n">
-        <x:v>3828.7026448751003</x:v>
-      </x:c>
-      <x:c r="F27" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G27" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H27" s="32" t="n">
-        <x:f>IF(E27=0,"",I27/E27)</x:f>
-        <x:v>665.6727229199573</x:v>
-      </x:c>
-      <x:c r="I27" s="31" t="n">
-        <x:f>IF(C27=0,"",SUMIF('Species'!$G$2:$G$347,A27,'Species'!$U$2:$U$347))</x:f>
-        <x:v>2548662.91486485</x:v>
-      </x:c>
-      <x:c r="J27" s="32" t="n">
-        <x:v>3.8228551790498573</x:v>
-      </x:c>
-      <x:c r="K27" s="32" t="n">
-        <x:f>IF(J27="","",(1/'Metadata'!$B$5)^(J27-1))</x:f>
-        <x:v>665.0513494955133</x:v>
-      </x:c>
-      <x:c r="L27" s="31" t="n">
-        <x:f>IF(E27=0,"",E27*K27)</x:f>
+        <x:f>IF(B27=0,"",B27*D27)</x:f>
         <x:v>2546283.8607912264</x:v>
       </x:c>
-      <x:c r="M27" s="31" t="n">
-        <x:f>IF(E27=0,"",I27-L27)</x:f>
-        <x:v>2379.054073623847</x:v>
-      </x:c>
-      <x:c r="N27" s="32" t="n">
-        <x:f>IF(L27=0,"",I27/L27)</x:f>
-        <x:v>1.000934323981021</x:v>
-      </x:c>
-      <x:c r="O27" s="34" t="n">
-        <x:f>IF(L27=0,"",M27/L27)</x:f>
-        <x:v>0.0009343239810209477</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G27">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O27">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0340bf1c0c694837"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re402c2d8fb54460d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26283,7 +24799,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -26382,7 +24898,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>1000014407.7534397</x:v>
+        <x:v>832607270.3364908</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -26396,7 +24912,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>1000014407.7534399</x:v>
+        <x:v>860984504.0341389</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -26410,7 +24926,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-2.384185791015625e-7</x:v>
+        <x:v>-167407137.41694915</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -26424,7 +24940,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-139029903.719301</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -26435,9 +24951,9 @@
         <x:v>EEZ_826</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -26449,47 +24965,19 @@
         <x:v>EEZ_826</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_826</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_826</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f6d4fa1df7544a0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdac57917f1b74047"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26536,7 +25024,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
